--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488055_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488055_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.679</v>
+        <v>5.4231</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8458</v>
+        <v>1.1514</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8332</v>
+        <v>4.2717</v>
       </c>
       <c r="G2" t="n">
         <v>1.1514</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6643</v>
+        <v>0.4083</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.624</v>
+        <v>-0.3184</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2883</v>
+        <v>0.7267</v>
       </c>
       <c r="V2" t="n">
         <v>1.8811</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8002</v>
+        <v>4.5716</v>
       </c>
       <c r="E3" t="n">
-        <v>3.496</v>
+        <v>2.9866</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3042</v>
+        <v>1.585</v>
       </c>
       <c r="G3" t="n">
         <v>2.95</v>
@@ -688,13 +688,13 @@
         <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6609</v>
+        <v>0.4323</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6095</v>
+        <v>0.1001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0514</v>
+        <v>0.3322</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2288</v>
+        <v>2.4854</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6746</v>
+        <v>1.1839</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5542</v>
+        <v>1.3015</v>
       </c>
       <c r="G4" t="n">
         <v>-2.0153</v>
@@ -766,13 +766,13 @@
         <v>2.5769</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3595</v>
+        <v>-0.1028</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2369</v>
+        <v>-0.7276</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.6247</v>
       </c>
       <c r="V4" t="n">
         <v>3.0178</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4714</v>
+        <v>1.8998</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7766</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6948</v>
+        <v>0.9194</v>
       </c>
       <c r="G5" t="n">
         <v>2.528</v>
@@ -844,13 +844,13 @@
         <v>1.9822</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.79</v>
+        <v>-0.3616</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8112</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0212</v>
+        <v>0.2458</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2666</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTIN GONZALEZ</t>
+          <t>A. BUALO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9619</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4657</v>
+        <v>0.2551</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3775</v>
+        <v>0.7068</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1462</v>
+        <v>1.4266</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5231</v>
+        <v>1.7825</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3769</v>
+        <v>-0.3559</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4703</v>
+        <v>1.5471</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9887</v>
+        <v>1.507</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5184</v>
+        <v>0.0402</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3241</v>
+        <v>-0.1205</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4656</v>
+        <v>0.2756</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1415</v>
+        <v>-0.3961</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7929</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>1.784</v>
+        <v>0.5947</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5059</v>
+        <v>0.1982</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0552</v>
+        <v>-0.301</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4507</v>
+        <v>0.4992</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5331</v>
+        <v>-0.2666</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5331</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8771</v>
+        <v>0.8282</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6776</v>
+        <v>-1.4739</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5548</v>
+        <v>2.302</v>
       </c>
       <c r="G7" t="n">
         <v>0.763</v>
@@ -1000,13 +1000,13 @@
         <v>2.9733</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1723</v>
+        <v>-0.2212</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0497</v>
+        <v>-0.846</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.6247</v>
       </c>
       <c r="V7" t="n">
         <v>1.2775</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BUALO</t>
+          <t>A. VAZQUEZ ASTILLEROS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8495</v>
+        <v>0.551</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2551</v>
+        <v>-1.3945</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5945</v>
+        <v>1.9455</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4266</v>
+        <v>0.0877</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7825</v>
+        <v>-0.9971</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3559</v>
+        <v>1.0848</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5471</v>
+        <v>1.4616</v>
       </c>
       <c r="K8" t="n">
-        <v>1.507</v>
+        <v>0.128</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>1.3336</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1205</v>
+        <v>-1.3739</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2756</v>
+        <v>-1.1251</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3961</v>
+        <v>-0.2488</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5947</v>
+        <v>3.7662</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0859</v>
+        <v>-0.5763</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.301</v>
+        <v>-0.7331</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3869</v>
+        <v>0.1568</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2666</v>
+        <v>-0.7444</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.1408</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2666</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ ASTILLEROS</t>
+          <t>J. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4002</v>
+        <v>0.5501</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2926</v>
+        <v>-0.7713</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6928</v>
+        <v>1.3214</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0877</v>
+        <v>0.1462</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9971</v>
+        <v>0.5231</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0848</v>
+        <v>-0.3769</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4616</v>
+        <v>0.4703</v>
       </c>
       <c r="K9" t="n">
-        <v>0.128</v>
+        <v>0.9887</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3336</v>
+        <v>-0.5184</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3739</v>
+        <v>-0.3241</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1251</v>
+        <v>-0.4656</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2488</v>
+        <v>0.1415</v>
       </c>
       <c r="P9" t="n">
+        <v>0.7929</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.784</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-1.9822</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3.7662</v>
-      </c>
       <c r="S9" t="n">
-        <v>-0.7272</v>
+        <v>0.1441</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6312</v>
+        <v>-0.2505</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0959</v>
+        <v>0.3946</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7444</v>
+        <v>-0.5331</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1408</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6036</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="10">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4719</v>
+        <v>-2.6195</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1508</v>
+        <v>-1.3546</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3211</v>
+        <v>-1.265</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3978</v>
@@ -1312,13 +1312,13 @@
         <v>0.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7276</v>
+        <v>0.58</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3782</v>
+        <v>0.1744</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3494</v>
+        <v>0.4056</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2071</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5158</v>
+        <v>-2.6738</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8533</v>
+        <v>-1.9552</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6625</v>
+        <v>-0.7186</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2958</v>
@@ -1390,13 +1390,13 @@
         <v>1.9822</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0485</v>
+        <v>-0.2065</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1944</v>
+        <v>-0.2963</v>
       </c>
       <c r="U12" t="n">
-        <v>0.146</v>
+        <v>0.0898</v>
       </c>
       <c r="V12" t="n">
         <v>1.8107</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3629</v>
+        <v>-4.1102</v>
       </c>
       <c r="E13" t="n">
         <v>-3.7487</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6142</v>
+        <v>-0.3615</v>
       </c>
       <c r="G13" t="n">
         <v>-1.629</v>
@@ -1468,13 +1468,13 @@
         <v>2.5769</v>
       </c>
       <c r="S13" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.3295</v>
       </c>
       <c r="T13" t="n">
         <v>-0.121</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1978</v>
+        <v>0.4505</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4142</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.170100000000001</v>
+        <v>8.170300000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.837899999999999</v>
+        <v>-3.8382</v>
       </c>
       <c r="F14" t="n">
         <v>12.0082</v>
@@ -1546,13 +1546,13 @@
         <v>22.7955</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6239000000000002</v>
+        <v>0.6239999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.9265</v>
+        <v>-3.926800000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>4.5508</v>
+        <v>4.5506</v>
       </c>
       <c r="V14" t="n">
         <v>2.5551</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8398</v>
+        <v>3.6991</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5446</v>
+        <v>3.1558</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2952</v>
+        <v>0.5434</v>
       </c>
       <c r="G15" t="n">
         <v>3.2267</v>
@@ -1624,13 +1624,13 @@
         <v>3.3698</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8428</v>
+        <v>0.0165</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4865</v>
+        <v>-0.8753</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6437</v>
+        <v>0.8918</v>
       </c>
       <c r="V15" t="n">
         <v>-0.337</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5269</v>
+        <v>2.8783</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1089</v>
+        <v>3.5164</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5819</v>
+        <v>-0.6381</v>
       </c>
       <c r="G16" t="n">
         <v>2.1475</v>
@@ -1702,13 +1702,13 @@
         <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4046</v>
+        <v>-0.0533</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.624</v>
+        <v>-0.2165</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2194</v>
+        <v>0.1632</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6036</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2868</v>
+        <v>0.3721</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7208</v>
+        <v>-1.6189</v>
       </c>
       <c r="F19" t="n">
-        <v>1.434</v>
+        <v>1.9911</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7295</v>
@@ -1936,13 +1936,13 @@
         <v>2.7751</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.791</v>
+        <v>-0.1321</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.745</v>
+        <v>-0.6431</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.046</v>
+        <v>0.511</v>
       </c>
       <c r="V19" t="n">
         <v>3.0178</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6061</v>
+        <v>-0.3018</v>
       </c>
       <c r="E20" t="n">
         <v>-0.7693</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1632</v>
+        <v>0.4675</v>
       </c>
       <c r="G20" t="n">
         <v>0.8096</v>
@@ -2014,13 +2014,13 @@
         <v>2.5769</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1968</v>
+        <v>0.5011</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3082</v>
       </c>
       <c r="U20" t="n">
-        <v>0.505</v>
+        <v>0.8093</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8107</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. TORIL RAYO</t>
+          <t>J. REYES ORTEGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0693</v>
+        <v>-1.0663</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7972</v>
+        <v>-2.163</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7279</v>
+        <v>1.0966</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3172</v>
+        <v>-1.2351</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.409</v>
+        <v>1.0664</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09180000000000001</v>
+        <v>-2.3015</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1409</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0605</v>
+        <v>1.9976</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0804</v>
+        <v>-1.9169</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4581</v>
+        <v>-1.3158</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4695</v>
+        <v>-0.9312</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0114</v>
+        <v>-0.3847</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.1805</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9911</v>
+        <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4372</v>
+        <v>-0.7718</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2423</v>
+        <v>-0.5964</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1949</v>
+        <v>-0.1754</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.9405</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. REYES ORTEGA</t>
+          <t>A. TORIL RAYO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4666</v>
+        <v>-1.3469</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3667</v>
+        <v>-2.1028</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9001</v>
+        <v>0.756</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2351</v>
+        <v>-0.3172</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0664</v>
+        <v>-0.409</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3015</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.1409</v>
       </c>
       <c r="K22" t="n">
-        <v>1.9976</v>
+        <v>0.0605</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9169</v>
+        <v>0.0804</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3158</v>
+        <v>-0.4581</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9312</v>
+        <v>-0.4695</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3847</v>
+        <v>0.0114</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.1805</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1805</v>
+        <v>0.9911</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1721</v>
+        <v>0.1597</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8001</v>
+        <v>-0.0633</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3719</v>
+        <v>0.223</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9405</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.4074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>I. VIVERO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0143</v>
+        <v>-2.4175</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8605</v>
+        <v>-2.8951</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1538</v>
+        <v>0.4776</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3014</v>
+        <v>-1.6008</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1846</v>
+        <v>-0.2042</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.486</v>
+        <v>-1.3966</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1207</v>
+        <v>-0.7527</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1609</v>
+        <v>0.5252</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0402</v>
+        <v>-1.2779</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1807</v>
+        <v>-0.8481</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3455</v>
+        <v>-0.7294</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5262</v>
+        <v>-0.1187</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3964</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3876</v>
+        <v>-2.5769</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2981</v>
+        <v>-0.0238</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0552</v>
+        <v>-0.7726</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2429</v>
+        <v>0.7488</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.6145</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.4074</v>
+        <v>1.2071</v>
       </c>
       <c r="X23" t="n">
         <v>-1.2071</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. VIVERO RODRIGUEZ</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7989</v>
+        <v>-2.6464</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6913</v>
+        <v>-2.268</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1075</v>
+        <v>-0.3785</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.6008</v>
+        <v>-0.3014</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2042</v>
+        <v>0.1846</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3966</v>
+        <v>-0.486</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7527</v>
+        <v>-0.1207</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5252</v>
+        <v>-0.1609</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2779</v>
+        <v>0.0402</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8481</v>
+        <v>-0.1807</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7294</v>
+        <v>0.3455</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1187</v>
+        <v>-0.5262</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7929</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.5769</v>
+        <v>-1.3876</v>
       </c>
       <c r="R24" t="n">
-        <v>1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4051</v>
+        <v>-0.334</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5688</v>
+        <v>-0.3523</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1637</v>
+        <v>0.0183</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.6145</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2071</v>
+        <v>-0.4074</v>
       </c>
       <c r="X24" t="n">
         <v>-1.2071</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8029</v>
+        <v>-8.169600000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.9638</v>
+        <v>-8.3713</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1609</v>
+        <v>0.2017</v>
       </c>
       <c r="G25" t="n">
         <v>-5.5254</v>
@@ -2404,13 +2404,13 @@
         <v>3.3698</v>
       </c>
       <c r="S25" t="n">
-        <v>2.0596</v>
+        <v>0.6928</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3154</v>
+        <v>-0.7229</v>
       </c>
       <c r="U25" t="n">
-        <v>2.375</v>
+        <v>1.4157</v>
       </c>
       <c r="V25" t="n">
         <v>-2.1476</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.170200000000001</v>
+        <v>-7.491000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-12.0081</v>
+        <v>-12.0082</v>
       </c>
       <c r="F26" t="n">
-        <v>3.838100000000001</v>
+        <v>4.5173</v>
       </c>
       <c r="G26" t="n">
         <v>-2.0176</v>
@@ -2482,19 +2482,19 @@
         <v>19.8223</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6239000000000003</v>
+        <v>0.05509999999999982</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.5505</v>
+        <v>-4.550599999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>3.9267</v>
+        <v>4.605700000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-2.5551</v>
       </c>
       <c r="W26" t="n">
-        <v>7.564500000000001</v>
+        <v>7.564500000000002</v>
       </c>
       <c r="X26" t="n">
         <v>-10.1196</v>
